--- a/utils/monday_sprint_sprint_2023-18.xlsx
+++ b/utils/monday_sprint_sprint_2023-18.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="170">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>21888</t>
+    <t>5053943106</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>25/08/2023</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>09/09/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,73 +102,85 @@
     <t>Agosto</t>
   </si>
   <si>
-    <t>21902</t>
+    <t>5053915037</t>
   </si>
   <si>
     <t>CONSULTA ROMANEIO - EXPEDIÇÃO</t>
   </si>
   <si>
-    <t>21878</t>
+    <t>30/08/2023</t>
+  </si>
+  <si>
+    <t>5053969003</t>
   </si>
   <si>
     <t>Registro de Inspeção</t>
   </si>
   <si>
-    <t>22013</t>
+    <t>5053226978</t>
   </si>
   <si>
     <t>Registro de Moldagem</t>
   </si>
   <si>
-    <t>21851</t>
+    <t>08/09/2023</t>
+  </si>
+  <si>
+    <t>5053996571</t>
   </si>
   <si>
     <t>Ajustes do Sistema de Controle de Peças Seriadas a serem destruídas</t>
   </si>
   <si>
-    <t>21861</t>
+    <t>5053988959</t>
   </si>
   <si>
     <t>Inclusão de Status Pré-Usinado em carteira</t>
   </si>
   <si>
-    <t>21587</t>
+    <t>03/09/2023</t>
+  </si>
+  <si>
+    <t>5054113945</t>
   </si>
   <si>
     <t>ALTERAÇÃO ID - LANÇAMENTO CUSTO EXPORTAÇÃO - SISTEMA INVOICE</t>
   </si>
   <si>
-    <t>22010</t>
+    <t>5053277188</t>
   </si>
   <si>
     <t>Melhorias lançamentos CTes</t>
   </si>
   <si>
-    <t>21569</t>
+    <t>5054141534</t>
   </si>
   <si>
     <t>REVISÃO FLUXO DE AC 101</t>
   </si>
   <si>
-    <t>21534</t>
+    <t>5054157902</t>
   </si>
   <si>
     <t>Relatório Alteração de carteira - Ajustes.</t>
   </si>
   <si>
-    <t>21512</t>
+    <t>29/08/2023</t>
+  </si>
+  <si>
+    <t>5054173537</t>
   </si>
   <si>
     <t>CRIAR FORMULÁRIO PARA SETOR 549 PRÉ PRODUTIVO</t>
   </si>
   <si>
-    <t>21982</t>
+    <t>5053459600</t>
   </si>
   <si>
     <t>Alteração Parcelas Sistema Invoice</t>
   </si>
   <si>
-    <t>21977</t>
+    <t>5053522735</t>
   </si>
   <si>
     <t>Chamado - Engenharia - Cópia de Análise Crítica</t>
@@ -177,25 +189,25 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>21499</t>
+    <t>5054190491</t>
   </si>
   <si>
     <t>Seq Estornadas - Destacar na consulta saldo dep</t>
   </si>
   <si>
-    <t>21949</t>
+    <t>5053541253</t>
   </si>
   <si>
     <t>Ajuste certificado de material</t>
   </si>
   <si>
-    <t>21933</t>
+    <t>5053597018</t>
   </si>
   <si>
     <t>Melhoria no sistema PCP – “sequências abertas por setor”</t>
   </si>
   <si>
-    <t>22050</t>
+    <t>5061700624</t>
   </si>
   <si>
     <t>Reordenar linhas do fluxo</t>
@@ -207,64 +219,67 @@
     <t>28/08/2023</t>
   </si>
   <si>
-    <t>21927</t>
+    <t>5053805204</t>
   </si>
   <si>
     <t>Habilitar coluna BOX no grid - EXPEDIÇÃO</t>
   </si>
   <si>
-    <t>21926</t>
+    <t>5053835960</t>
   </si>
   <si>
     <t>QVD Follow-Up</t>
   </si>
   <si>
-    <t>21925</t>
+    <t>5053856556</t>
   </si>
   <si>
     <t>QVD Ordem de compra</t>
   </si>
   <si>
-    <t>21903</t>
+    <t>5053879345</t>
   </si>
   <si>
     <t>INCLUIR DADOS DE APONTAMENTO ELETRONICO NO QLIKSENSE</t>
   </si>
   <si>
-    <t>22009</t>
+    <t>5053345916</t>
   </si>
   <si>
     <t>Ajuste valor ICMS ST</t>
   </si>
   <si>
-    <t>21928</t>
+    <t>5063342594</t>
   </si>
   <si>
     <t>Criar grupo econômico de cliente para inventariar (manter a opção de inventário individual</t>
   </si>
   <si>
+    <t>5063349445</t>
+  </si>
+  <si>
     <t>Tabela dinâmica inventário por cliente</t>
   </si>
   <si>
-    <t>21168</t>
+    <t>5071192867</t>
   </si>
   <si>
     <t>Melhorias nos formulários de Análise Crítica</t>
   </si>
   <si>
-    <t>29/08/2023</t>
+    <t>05/09/2023</t>
   </si>
   <si>
     <t>Semana 5</t>
   </si>
   <si>
-    <t>21915</t>
+    <t>5053864142</t>
   </si>
   <si>
     <t>Novos setores - END's ISO 9712</t>
   </si>
   <si>
-    <t>21526</t>
+    <t>4901504794</t>
   </si>
   <si>
     <t>Desenvolver relatório analítico por sequência</t>
@@ -273,10 +288,13 @@
     <t>31/07/2023</t>
   </si>
   <si>
+    <t>07/09/2023</t>
+  </si>
+  <si>
     <t>Julho</t>
   </si>
   <si>
-    <t>19402</t>
+    <t>4735299081</t>
   </si>
   <si>
     <t>Análise</t>
@@ -291,7 +309,7 @@
     <t>Junho</t>
   </si>
   <si>
-    <t>22014</t>
+    <t>5053185296</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -300,25 +318,31 @@
     <t>Análise de API's Integração NIMBI x ERP Altona</t>
   </si>
   <si>
-    <t>22029</t>
+    <t>5054723934</t>
   </si>
   <si>
     <t>Atualização de usuários - Altona Multiacervo</t>
   </si>
   <si>
-    <t>18941</t>
+    <t>10/09/2023</t>
+  </si>
+  <si>
+    <t>5061623114</t>
   </si>
   <si>
     <t>Produtivo em horas</t>
   </si>
   <si>
-    <t>22006</t>
+    <t>5053435952</t>
   </si>
   <si>
     <t>Sistema de desmoldagem</t>
   </si>
   <si>
-    <t>21798</t>
+    <t>04/09/2023</t>
+  </si>
+  <si>
+    <t>5090996183</t>
   </si>
   <si>
     <t>Consultar sequencias trabalhadas no dia (por data e operador)</t>
@@ -333,25 +357,43 @@
     <t>Setembro</t>
   </si>
   <si>
+    <t>5090998671</t>
+  </si>
+  <si>
     <t>Verificar encerramento de operação em aberto, quando usuário encerrar o turno (consistir cartão ponto)</t>
   </si>
   <si>
+    <t>5091000497</t>
+  </si>
+  <si>
     <t>Incluir indicador no tipo de atividade para solicitar ou não a aprovação</t>
   </si>
   <si>
+    <t>5091002543</t>
+  </si>
+  <si>
     <t>Criar tela para editar e aprovar o apontamento</t>
   </si>
   <si>
+    <t>5091003713</t>
+  </si>
+  <si>
     <t>Controlar quando o operador iniciar apontamento em nova sequencia sem fechar a anterior</t>
   </si>
   <si>
+    <t>5091005230</t>
+  </si>
+  <si>
     <t>Informar a quantidade de peças, para o caso de lote da mesma sequencia</t>
   </si>
   <si>
+    <t>5091006827</t>
+  </si>
+  <si>
     <t>Abrir grid para informar mais sequencias (para rateio do tempo) e emitir alerta quando modelo diferente da sequencia principal</t>
   </si>
   <si>
-    <t>21887</t>
+    <t>5053958946</t>
   </si>
   <si>
     <t>Melhoria no sistema de tratamento térmico</t>
@@ -369,19 +411,19 @@
     <t>Não definida</t>
   </si>
   <si>
+    <t>10/04/2023</t>
+  </si>
+  <si>
     <t>A fazer</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
     <t>5063221585</t>
   </si>
   <si>
     <t>5063221909</t>
   </si>
   <si>
-    <t>21423</t>
+    <t>5005100122</t>
   </si>
   <si>
     <t>Bloquear impressão</t>
@@ -399,7 +441,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-18</t>
+    <t>Jun/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -454,6 +496,9 @@
   </si>
   <si>
     <t>Sim</t>
+  </si>
+  <si>
+    <t>Semana 2</t>
   </si>
   <si>
     <t>Abertos</t>
@@ -1038,7 +1083,7 @@
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1055,7 +1100,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1067,10 +1112,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1102,7 +1147,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1114,10 +1159,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1132,7 +1177,7 @@
         <v>23</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1149,7 +1194,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1161,10 +1206,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1196,7 +1241,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1208,10 +1253,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1226,7 +1271,7 @@
         <v>23</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1243,7 +1288,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1255,10 +1300,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1273,7 +1318,7 @@
         <v>23</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1290,7 +1335,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1302,10 +1347,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1320,7 +1365,7 @@
         <v>23</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1337,7 +1382,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1349,10 +1394,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1384,7 +1429,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1396,10 +1441,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1414,7 +1459,7 @@
         <v>23</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1431,7 +1476,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1443,10 +1488,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1478,7 +1523,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1490,10 +1535,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1508,7 +1553,7 @@
         <v>23</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1525,7 +1570,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1537,13 +1582,13 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>21</v>
@@ -1572,7 +1617,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1584,10 +1629,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1602,7 +1647,7 @@
         <v>23</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1619,7 +1664,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1631,10 +1676,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1649,7 +1694,7 @@
         <v>23</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1666,7 +1711,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1678,10 +1723,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1713,7 +1758,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1725,13 +1770,13 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>21</v>
@@ -1740,7 +1785,7 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>24</v>
@@ -1760,7 +1805,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1772,10 +1817,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1790,7 +1835,7 @@
         <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1807,7 +1852,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1819,10 +1864,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1837,7 +1882,7 @@
         <v>23</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1854,7 +1899,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1866,10 +1911,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1884,7 +1929,7 @@
         <v>23</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1901,7 +1946,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1913,10 +1958,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1948,7 +1993,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1960,10 +2005,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1978,7 +2023,7 @@
         <v>23</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1995,7 +2040,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2007,10 +2052,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2022,10 +2067,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2042,7 +2087,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2054,10 +2099,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2069,7 +2114,7 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>24</v>
@@ -2089,7 +2134,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2101,10 +2146,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2116,10 +2161,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2128,7 +2173,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>28</v>
@@ -2136,7 +2181,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2148,10 +2193,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2166,7 +2211,7 @@
         <v>23</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2183,7 +2228,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2195,10 +2240,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2210,42 +2255,42 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N28" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="K28" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="O28" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2257,10 +2302,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2269,33 +2314,33 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>21</v>
@@ -2307,7 +2352,7 @@
         <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2324,7 +2369,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2336,10 +2381,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2354,7 +2399,7 @@
         <v>23</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2371,25 +2416,25 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>21</v>
@@ -2398,7 +2443,7 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>24</v>
@@ -2418,22 +2463,22 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2448,7 +2493,7 @@
         <v>23</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2465,22 +2510,22 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2492,10 +2537,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2504,30 +2549,30 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2539,10 +2584,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2551,30 +2596,30 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2586,10 +2631,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2598,30 +2643,30 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2633,11 +2678,11 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="K37" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="K37" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
       </c>
@@ -2645,30 +2690,30 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2680,10 +2725,10 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2692,30 +2737,30 @@
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2727,10 +2772,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2739,45 +2784,45 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J40" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F40" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2786,15 +2831,15 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2806,10 +2851,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -2841,25 +2886,25 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>21</v>
@@ -2868,16 +2913,16 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>27</v>
@@ -2888,25 +2933,25 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>21</v>
@@ -2915,16 +2960,16 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>27</v>
@@ -2935,25 +2980,25 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>21</v>
@@ -2962,16 +3007,16 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>27</v>
@@ -2982,7 +3027,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -2994,10 +3039,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3009,10 +3054,10 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3021,7 +3066,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>28</v>
@@ -3040,23 +3085,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3064,16 +3109,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3084,7 +3129,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>13.76</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -3092,7 +3137,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3105,7 +3150,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -3113,7 +3158,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3144,12 +3189,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B2">
         <v>44</v>
@@ -3163,7 +3208,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3173,25 +3218,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3208,13 +3253,13 @@
         <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3226,7 +3271,7 @@
         <v>41</v>
       </c>
       <c r="P10" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3234,13 +3279,13 @@
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -3249,24 +3294,24 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M11" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="N11">
         <v>3</v>
       </c>
       <c r="P11" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -3278,13 +3323,13 @@
         <v>37</v>
       </c>
       <c r="J12" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="K12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -3293,44 +3338,44 @@
         <v>27</v>
       </c>
       <c r="Q12">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3338,7 +3383,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3346,7 +3391,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3354,7 +3399,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3362,10 +3407,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3373,7 +3418,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3381,142 +3426,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>128</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>1069</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>1069</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>135</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>1069</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>36</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>38</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
